--- a/outputs/Block2_Architecture_Contract_v12.xlsx
+++ b/outputs/Block2_Architecture_Contract_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Order</t>
   </si>
@@ -40,7 +40,7 @@
     <t>National nested selector</t>
   </si>
   <si>
-    <t>Constraint and identity engine</t>
+    <t>Compatibility / accounting bridge</t>
   </si>
   <si>
     <t>Five-model 2026 jackknife</t>
@@ -55,10 +55,10 @@
     <t>Monte Carlo</t>
   </si>
   <si>
-    <t>71 pre-election inputs</t>
-  </si>
-  <si>
-    <t>34 frozen raw targets + institutional totals</t>
+    <t>42 production pre-election inputs</t>
+  </si>
+  <si>
+    <t>DPP/RPP + institutional chamber baselines</t>
   </si>
   <si>
     <t>Five four-cycle refits</t>
@@ -73,16 +73,16 @@
     <t>Frozen point estimates and validated uncertainty</t>
   </si>
   <si>
-    <t>34 learned targets</t>
-  </si>
-  <si>
-    <t>All 42 national targets</t>
+    <t>2 learned national outcomes (DPP/RPP)</t>
+  </si>
+  <si>
+    <t>8 temporary compatibility/accounting fields; authoritative chamber values are overwritten downstream from races</t>
   </si>
   <si>
     <t>Mean, median, range and deletion sensitivity</t>
   </si>
   <si>
-    <t>Single national production forecast</t>
+    <t>Single DPP/RPP production forecast</t>
   </si>
   <si>
     <t>Race margins, probabilities and canonical Senate total</t>
@@ -94,13 +94,13 @@
     <t>Constraint/identity engine</t>
   </si>
   <si>
-    <t>National dashboard and downstream Senate context</t>
+    <t>Report/HTML compatibility only until race-first House/Senate overwrite</t>
   </si>
   <si>
     <t>Diagnostics only</t>
   </si>
   <si>
-    <t>Monte Carlo and state-Senate context</t>
+    <t>Frozen national context for House/Senate; never chamber quotas</t>
   </si>
   <si>
     <t>Senate dashboard and simulation</t>
@@ -112,7 +112,7 @@
     <t>Its own training rows</t>
   </si>
   <si>
-    <t>National model selection</t>
+    <t>National model selection or any race winner</t>
   </si>
   <si>
     <t>Training, target values or production point forecast</t>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>Upstream</t>
+  </si>
+  <si>
+    <t>Bridge only</t>
   </si>
   <si>
     <t>Diagnostic only</t>
@@ -566,7 +569,7 @@
         <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -589,7 +592,7 @@
         <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -612,7 +615,7 @@
         <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -635,7 +638,7 @@
         <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -658,7 +661,7 @@
         <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
